--- a/output/graficos_nacionales/plot_nacional_sexo_e_rezjov_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_sexo_e_rezjov_a_2021.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 15:14</t>
+    <t xml:space="preserve">2026-10-01 16:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_sexo_e_rezjov_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_sexo_e_rezjov_a_2021.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 16:35</t>
+    <t xml:space="preserve">2026-10-01 19:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_sexo_e_rezjov_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_sexo_e_rezjov_a_2021.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:22</t>
+    <t xml:space="preserve">2026-10-01 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_sexo_e_rezjov_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_sexo_e_rezjov_a_2021.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:11</t>
+    <t xml:space="preserve">2026-10-05 06:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -559,7 +559,7 @@
         <v>3.3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="6">
